--- a/01-02-02/top3-form-blank.xlsx
+++ b/01-02-02/top3-form-blank.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0;-0;;@"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -101,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,13 +123,16 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -672,7 +677,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D5:D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,매주,매달"</formula1>
+      <formula1>"매일,주 몇 번,매주,매달"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -844,27 +849,27 @@
           <t>합계</t>
         </is>
       </c>
-      <c r="B15" s="8">
-        <f>SUM(B5:B14)</f>
+      <c r="B15" s="9">
+        <f>IF(SUM(B5:B14)=0,"",SUM(B5:B14))</f>
         <v/>
       </c>
-      <c r="C15" s="9">
-        <f>IF(B15=100,"100 맞아요","합계를 100으로 맞춰요")</f>
+      <c r="C15" s="10">
+        <f>IF(B15="","",IF(B15=100,"100 맞아요","합계를 100으로 맞춰요"))</f>
         <v/>
       </c>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>별표 세 개 넘기면 돌아오는 시간</t>
         </is>
       </c>
-      <c r="B16" s="11">
-        <f>SUMIF(G5:G14,"★*",B5:B14)</f>
+      <c r="B16" s="12">
+        <f>IF(SUMIF(G5:G14,"★*",B5:B14)=0,"",SUMIF(G5:G14,"★*",B5:B14))</f>
         <v/>
       </c>
       <c r="C16" s="4" t="n"/>
@@ -879,12 +884,22 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C15:E15"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation sqref="E5:E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1단계,2단계,3단계"</formula1>
     </dataValidation>
     <dataValidation sqref="G5:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"★1,★2,★3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"매일,주 몇 번,매주,매달"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0.5시간,1시간,2시간"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5:B14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="숫자만" error="0에서 100 사이 숫자만 적어요." type="whole" errorStyle="warning" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -924,7 +939,7 @@
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>내 시간 중 몇 %</t>
         </is>
@@ -936,7 +951,7 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>얼마나 자주</t>
         </is>
@@ -948,7 +963,7 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>한 번에 몇 시간</t>
         </is>
@@ -960,7 +975,7 @@
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>얼마나 단순한가 1단계</t>
         </is>
@@ -972,7 +987,7 @@
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>얼마나 단순한가 2단계</t>
         </is>
@@ -984,7 +999,7 @@
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>얼마나 단순한가 3단계</t>
         </is>
@@ -996,7 +1011,7 @@
       </c>
     </row>
     <row r="10" ht="66" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>누구에게</t>
         </is>
@@ -1008,7 +1023,7 @@
       </c>
     </row>
     <row r="11" ht="66" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TOP3 ★ 고르는 법</t>
         </is>

--- a/01-02-02/top3-form-blank.xlsx
+++ b/01-02-02/top3-form-blank.xlsx
@@ -677,7 +677,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D5:D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 몇 번,매주,매달"</formula1>
+      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -892,10 +892,10 @@
       <formula1>"★1,★2,★3"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 몇 번,매주,매달"</formula1>
+      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"0.5시간,1시간,2시간"</formula1>
+      <formula1>"0.5시간,1시간,2시간,2시간 이상"</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="숫자만" error="0에서 100 사이 숫자만 적어요." type="whole" errorStyle="warning" operator="between">
       <formula1>0</formula1>

--- a/01-02-02/top3-form-blank.xlsx
+++ b/01-02-02/top3-form-blank.xlsx
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,7 +119,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -638,28 +637,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -844,31 +843,31 @@
       <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="8">
         <f>IF(SUM(B5:B14)=0,"",SUM(B5:B14))</f>
         <v/>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <f>IF(B15="","",IF(B15=100,"100 맞아요","합계를 100으로 맞춰요"))</f>
         <v/>
       </c>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>별표 세 개 넘기면 돌아오는 시간</t>
         </is>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <f>IF(SUMIF(G5:G14,"★*",B5:B14)=0,"",SUMIF(G5:G14,"★*",B5:B14))</f>
         <v/>
       </c>
@@ -939,7 +938,7 @@
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>내 시간 중 몇 %</t>
         </is>
@@ -951,7 +950,7 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>얼마나 자주</t>
         </is>
@@ -963,7 +962,7 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>한 번에 몇 시간</t>
         </is>
@@ -975,7 +974,7 @@
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>얼마나 단순한가 1단계</t>
         </is>
@@ -987,7 +986,7 @@
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>얼마나 단순한가 2단계</t>
         </is>
@@ -999,7 +998,7 @@
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>얼마나 단순한가 3단계</t>
         </is>
@@ -1011,7 +1010,7 @@
       </c>
     </row>
     <row r="10" ht="66" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>누구에게</t>
         </is>
@@ -1023,7 +1022,7 @@
       </c>
     </row>
     <row r="11" ht="66" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>TOP3 ★ 고르는 법</t>
         </is>

--- a/01-02-02/top3-form-blank.xlsx
+++ b/01-02-02/top3-form-blank.xlsx
@@ -674,8 +674,11 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A23:D23"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D5:D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D18:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
   </dataValidations>

--- a/01-02-02/top3-form-blank.xlsx
+++ b/01-02-02/top3-form-blank.xlsx
@@ -77,7 +77,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -99,11 +99,55 @@
         <color rgb="00DCD1C1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DCD1C1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DCD1C1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DCD1C1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DCD1C1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -137,6 +181,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,6 +571,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -607,6 +654,7 @@
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -660,6 +708,7 @@
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -714,14 +763,15 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1장에서 적은 일을 비슷한 것끼리 묶어 「하는 일」 칸에 한 줄씩 옮겨요.</t>
-        </is>
-      </c>
-    </row>
+          <t>1장에 적은 일을 「하는 일」 칸에 옮겨요. 같은 일은 한 줄로 모아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>하는 일 (묶음)</t>
+          <t>하는 일</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -859,15 +909,15 @@
         <f>IF(B15="","",IF(B15=100,"100 맞아요","합계를 100으로 맞춰요"))</f>
         <v/>
       </c>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="14" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>별표 세 개 넘기면 돌아오는 시간</t>
+          <t>TOP3 합계</t>
         </is>
       </c>
       <c r="B16" s="11">
@@ -928,6 +978,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1078,7 @@
     <row r="11" ht="66" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>TOP3 ★ 고르는 법</t>
+          <t>별표 치는 순서</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">

--- a/01-02-02/top3-form-blank.xlsx
+++ b/01-02-02/top3-form-blank.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>매일 / 매주 / 매달</t>
+          <t>매일 / 주 몇 번</t>
         </is>
       </c>
     </row>
@@ -725,10 +725,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D5:D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
+      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번"</formula1>
     </dataValidation>
     <dataValidation sqref="D18:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
+      <formula1>"매주,매달"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -944,7 +944,7 @@
       <formula1>"★1,★2,★3"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
+      <formula1>"매일,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0.5시간,1시간,2시간,2시간 이상"</formula1>
@@ -999,7 +999,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>일주일 동안 내가 일한 시간을 100으로 놓고 이 일이 얼마를 먹는지 느낌으로 적어요. 5 · 10 단위면 충분해요.</t>
+          <t>일주일 동안 내가 일한 시간을 100으로 놓고 이 일이 얼마를 먹는지 대충 적어요. 5 · 10 단위면 충분해요.</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>① 3단계는 빼요. ② 매일 하고, 하루 30분 이상 붙잡고, 1단계인 일은 %가 작아도 먼저 ★를 줘요(여러 개면 % 큰 순서). ③ 남은 것은 % 큰 순서로 ★를 이어 줘요. ④ %가 같으면 1단계 먼저, 그래도 같으면 더 자주 하는 일 먼저예요.</t>
+          <t>1. 3단계는 빼요. 2. 매일 하고, 하루 30분 이상 붙잡고, 1단계인 일은 %가 작아도 먼저 ★를 줘요(여러 개면 % 큰 순서). 3. 남은 것은 % 큰 순서로 ★를 이어 줘요. 4. %가 같으면 1단계 먼저, 그래도 같으면 더 자주 하는 일 먼저예요.</t>
         </is>
       </c>
     </row>
